--- a/관광e배움터_data.xlsx
+++ b/관광e배움터_data.xlsx
@@ -21780,12 +21780,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F0ED"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEBEEEC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>

--- a/관광e배움터_data.xlsx
+++ b/관광e배움터_data.xlsx
@@ -21775,7 +21775,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF106A63"/>
+        <fgColor rgb="FF92400E"/>
       </patternFill>
     </fill>
     <fill>
@@ -22589,7 +22589,7 @@
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF106A63"/>
+        <color rgb="FF92400E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -22603,7 +22603,7 @@
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF106A63"/>
+        <color rgb="FF92400E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -22617,7 +22617,7 @@
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF106A63"/>
+        <color rgb="FF92400E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
@@ -22631,7 +22631,7 @@
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF106A63"/>
+        <color rgb="FF92400E"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">

--- a/관광e배움터_data.xlsx
+++ b/관광e배움터_data.xlsx
@@ -22183,11 +22183,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
   <dimension ref="A1:B57"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.375" customWidth="1"/>
@@ -22212,7 +22209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -22220,7 +22217,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="6" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -22228,7 +22225,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -22249,7 +22246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -22257,7 +22254,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -22265,7 +22262,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -22273,7 +22270,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -22281,7 +22278,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -22289,7 +22286,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -22297,7 +22294,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -22305,7 +22302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -22313,7 +22310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -22321,7 +22318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -22342,7 +22339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -22350,7 +22347,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="27" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -22358,7 +22355,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="28" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -22366,7 +22363,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="29" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -22374,7 +22371,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -22382,7 +22379,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -22390,7 +22387,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -22398,7 +22395,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -22419,7 +22416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>27</v>
       </c>
@@ -22427,7 +22424,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="39" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -22435,7 +22432,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="40" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -22443,7 +22440,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="41" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>30</v>
       </c>
@@ -22451,7 +22448,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="42" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>31</v>
       </c>
@@ -22459,7 +22456,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="43" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -22467,7 +22464,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="44" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -22475,7 +22472,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="45" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -22483,7 +22480,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="46" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>35</v>
       </c>
@@ -22491,7 +22488,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>36</v>
       </c>
@@ -22499,7 +22496,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="48" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -22507,7 +22504,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>38</v>
       </c>
@@ -22515,7 +22512,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -22523,7 +22520,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -22531,7 +22528,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>41</v>
       </c>
@@ -22539,7 +22536,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>42</v>
       </c>
@@ -22547,7 +22544,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>43</v>
       </c>
@@ -22555,7 +22552,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>44</v>
       </c>
@@ -22563,7 +22560,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>45</v>
       </c>
@@ -22571,7 +22568,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>46</v>
       </c>
